--- a/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
+++ b/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
@@ -1334,7 +1334,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>channels.csv VRC_REAR_OUT Gnd Rear out (GNDOUT)</t>
+          <t>channels.csv VRC_REAR_OUT Gnd Rear out (GNDOUT_B)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -2246,10 +2246,14 @@
       <c r="AB12" s="53" t="inlineStr"/>
       <c r="AC12" s="54" t="inlineStr"/>
       <c r="AD12" s="54" t="inlineStr"/>
-      <c r="AE12" s="54" t="inlineStr"/>
+      <c r="AE12" s="54" t="inlineStr">
+        <is>
+          <t>splice I6r1ot: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF12" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice I6r1ot is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG12" s="54" t="inlineStr">
@@ -2357,10 +2361,14 @@
       <c r="AB13" s="37" t="inlineStr"/>
       <c r="AC13" s="38" t="inlineStr"/>
       <c r="AD13" s="38" t="inlineStr"/>
-      <c r="AE13" s="38" t="inlineStr"/>
+      <c r="AE13" s="38" t="inlineStr">
+        <is>
+          <t>splice I6r1ot: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF13" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice I6r1ot is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG13" s="38" t="inlineStr">
@@ -2474,12 +2482,12 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>channels.csv VRC_REAR_IN_L 3 Rear in L screen (SHIELD_B)</t>
+          <t>splice I6r1ot: node of the wire list (SoT); channels.csv VRC_REAR_IN_L 3 Rear in L screen (SHIELD_B)</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice I6r1ot is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG14" s="54" t="inlineStr"/>
@@ -2759,7 +2767,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
+++ b/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
@@ -746,7 +746,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -763,7 +763,7 @@
     <col width="36" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>I6r1ot</t>
+          <t>sp_ws_r_shield</t>
         </is>
       </c>
       <c r="G12" s="42" t="inlineStr">
         <is>
-          <t>splice I6r1ot (Sensor screen join)</t>
+          <t>splice sp_ws_r_shield (Sensor screen join)</t>
         </is>
       </c>
       <c r="H12" s="41" t="inlineStr"/>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="S12" s="48" t="inlineStr">
         <is>
-          <t>I6r1ot</t>
+          <t>sp_ws_r_shield</t>
         </is>
       </c>
       <c r="T12" s="48" t="inlineStr">
@@ -2248,7 +2248,7 @@
       <c r="AD12" s="54" t="inlineStr"/>
       <c r="AE12" s="54" t="inlineStr">
         <is>
-          <t>splice I6r1ot: node of the wire list (SoT)</t>
+          <t>splice sp_ws_r_shield: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF12" s="54" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>I6r1ot</t>
+          <t>sp_ws_r_shield</t>
         </is>
       </c>
       <c r="G13" s="26" t="inlineStr">
         <is>
-          <t>splice I6r1ot (Sensor screen join)</t>
+          <t>splice sp_ws_r_shield (Sensor screen join)</t>
         </is>
       </c>
       <c r="H13" s="25" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
-          <t>I6r1ot</t>
+          <t>sp_ws_r_shield</t>
         </is>
       </c>
       <c r="T13" s="32" t="inlineStr">
@@ -2363,7 +2363,7 @@
       <c r="AD13" s="38" t="inlineStr"/>
       <c r="AE13" s="38" t="inlineStr">
         <is>
-          <t>splice I6r1ot: node of the wire list (SoT)</t>
+          <t>splice sp_ws_r_shield: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF13" s="38" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="B14" s="39" t="inlineStr">
         <is>
-          <t>_TXY7m</t>
+          <t>w_ws_r_shield</t>
         </is>
       </c>
       <c r="C14" s="39" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>I6r1ot</t>
+          <t>sp_ws_r_shield</t>
         </is>
       </c>
       <c r="G14" s="42" t="inlineStr">
         <is>
-          <t>splice I6r1ot (Sensor screen join)</t>
+          <t>splice sp_ws_r_shield (Sensor screen join)</t>
         </is>
       </c>
       <c r="H14" s="41" t="inlineStr"/>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="S14" s="48" t="inlineStr">
         <is>
-          <t>I6r1ot</t>
+          <t>sp_ws_r_shield</t>
         </is>
       </c>
       <c r="T14" s="48" t="inlineStr"/>
@@ -2482,7 +2482,7 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>splice I6r1ot: node of the wire list (SoT); channels.csv VRC_REAR_IN_L 3 Rear in L screen (SHIELD_B)</t>
+          <t>splice sp_ws_r_shield: node of the wire list (SoT); channels.csv VRC_REAR_IN_L 3 Rear in L screen (SHIELD_B)</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2577,7 +2577,7 @@
   <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -2718,7 +2718,7 @@
     <row r="3">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>I6r1ot</t>
+          <t>sp_ws_r_shield</t>
         </is>
       </c>
       <c r="B3" s="55" t="inlineStr">

--- a/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
+++ b/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
@@ -2461,14 +2461,10 @@
       </c>
       <c r="V14" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W14" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W14" s="50" t="inlineStr"/>
       <c r="X14" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow</t>

--- a/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
+++ b/docs/harness/wirelist/WheelSpeed-Rear-wirelist.xlsx
@@ -2787,7 +2787,7 @@
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
-          <t>ix_ws_rear_p on B-cabin</t>
+          <t>ix_ws_rear_p on ECU-cabin</t>
         </is>
       </c>
       <c r="F5" s="33" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="E3" s="27" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="E4" s="43" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F4" s="44" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="E5" s="27" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E6" s="43" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F6" s="44" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
-          <t>B-cabin</t>
+          <t>ECU-cabin</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
